--- a/Master/2256r2/2256r2 @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/2256r2/2256r2 @ 0.250 IPR_cutlet_data.xlsx
@@ -2034,622 +2034,622 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>5.247</v>
+        <v>1.263</v>
       </c>
       <c r="B80" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C80" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>6.8783</v>
+        <v>6.85</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>-1.3459</v>
+        <v>-3.5806</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>0.0018</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>4.148</v>
+        <v>5.247</v>
       </c>
       <c r="B81" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C81" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>6.8828</v>
+        <v>6.8783</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>-1.4818</v>
+        <v>-1.3459</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>0.0133</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
-        <v>4.248</v>
+        <v>4.148</v>
       </c>
       <c r="B82" s="6" t="n">
         <v>4</v>
       </c>
       <c r="C82" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>6.9335</v>
+        <v>6.8828</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>-1.5091</v>
+        <v>-1.4818</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>0.0018</v>
+        <v>0.0133</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
-        <v>3.149</v>
+        <v>4.248</v>
       </c>
       <c r="B83" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C83" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>6.9386</v>
+        <v>6.9335</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>-1.6537</v>
+        <v>-1.5091</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>0.0114</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
-        <v>3.249</v>
+        <v>3.149</v>
       </c>
       <c r="B84" s="6" t="n">
         <v>3</v>
       </c>
       <c r="C84" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D84" s="7" t="n">
-        <v>6.9834</v>
+        <v>6.9386</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>-1.6798</v>
+        <v>-1.6537</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>0.0018</v>
+        <v>0.0114</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
-        <v>2.15</v>
+        <v>3.249</v>
       </c>
       <c r="B85" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C85" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>6.9909</v>
+        <v>6.9834</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-1.8308</v>
+        <v>-1.6798</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>0.0104</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="B86" s="6" t="n">
         <v>2</v>
       </c>
       <c r="C86" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D86" s="7" t="n">
-        <v>7.0284</v>
+        <v>6.9909</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>-1.8499</v>
+        <v>-1.8308</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>0.0019</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
-        <v>1.151</v>
+        <v>2.25</v>
       </c>
       <c r="B87" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>7.0343</v>
+        <v>7.0284</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>-2.0014</v>
+        <v>-1.8499</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>0.0077</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
-        <v>1.251</v>
+        <v>1.151</v>
       </c>
       <c r="B88" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C88" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>7.0662</v>
+        <v>7.0343</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>-2.0204</v>
+        <v>-2.0014</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>0.0019</v>
+        <v>0.0077</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
-        <v>6.152</v>
+        <v>1.251</v>
       </c>
       <c r="B89" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C89" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>7.0734</v>
+        <v>7.0662</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>-1.9166</v>
+        <v>-2.0204</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>0.0071</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>6.252</v>
+        <v>6.152</v>
       </c>
       <c r="B90" s="6" t="n">
         <v>6</v>
       </c>
       <c r="C90" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90" s="7" t="n">
-        <v>7.1025</v>
+        <v>7.0734</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>-1.9339</v>
+        <v>-1.9166</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>0.0019</v>
+        <v>0.0071</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
-        <v>5.153</v>
+        <v>6.252</v>
       </c>
       <c r="B91" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C91" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>7.1072</v>
+        <v>7.1025</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>-2.0787</v>
+        <v>-1.9339</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>0.0066</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
-        <v>5.253</v>
+        <v>5.153</v>
       </c>
       <c r="B92" s="6" t="n">
         <v>5</v>
       </c>
       <c r="C92" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92" s="7" t="n">
-        <v>7.1362</v>
+        <v>7.1072</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>-2.1003</v>
+        <v>-2.0787</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>0.0019</v>
+        <v>0.0066</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
-        <v>4.154</v>
+        <v>5.253</v>
       </c>
       <c r="B93" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C93" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>7.1408</v>
+        <v>7.1362</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>-2.2461</v>
+        <v>-2.1003</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>0.0064</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
-        <v>4.254</v>
+        <v>4.154</v>
       </c>
       <c r="B94" s="6" t="n">
         <v>4</v>
       </c>
       <c r="C94" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" s="7" t="n">
-        <v>7.168</v>
+        <v>7.1408</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>-2.2661</v>
+        <v>-2.2461</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>0.0019</v>
+        <v>0.0064</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>3.155</v>
+        <v>4.254</v>
       </c>
       <c r="B95" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C95" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>7.1723</v>
+        <v>7.168</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>-2.4161</v>
+        <v>-2.2661</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>0.0056</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
-        <v>3.255</v>
+        <v>3.155</v>
       </c>
       <c r="B96" s="6" t="n">
         <v>3</v>
       </c>
       <c r="C96" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D96" s="7" t="n">
-        <v>7.1978</v>
+        <v>7.1723</v>
       </c>
       <c r="E96" s="7" t="n">
-        <v>-2.4368</v>
+        <v>-2.4161</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>0.0019</v>
+        <v>0.0056</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
-        <v>2.156</v>
+        <v>3.255</v>
       </c>
       <c r="B97" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C97" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>7.2021</v>
+        <v>7.1978</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>-2.5884</v>
+        <v>-2.4368</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>0.0053</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
-        <v>2.256</v>
+        <v>2.156</v>
       </c>
       <c r="B98" s="6" t="n">
         <v>2</v>
       </c>
       <c r="C98" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D98" s="7" t="n">
-        <v>7.2259</v>
+        <v>7.2021</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>-2.6076</v>
+        <v>-2.5884</v>
       </c>
       <c r="F98" s="7" t="n">
-        <v>0.0019</v>
+        <v>0.0053</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
-        <v>1.157</v>
+        <v>2.256</v>
       </c>
       <c r="B99" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>7.2293</v>
+        <v>7.2259</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>-2.7587</v>
+        <v>-2.6076</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>0.0045</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>1.257</v>
+        <v>1.157</v>
       </c>
       <c r="B100" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C100" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D100" s="7" t="n">
-        <v>7.2514</v>
+        <v>7.2293</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>-2.7786</v>
+        <v>-2.7587</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>0.0018</v>
+        <v>0.0045</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
-        <v>6.158</v>
+        <v>1.257</v>
       </c>
       <c r="B101" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C101" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>7.2544</v>
+        <v>7.2514</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>-2.6777</v>
+        <v>-2.7786</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>0.0043</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
-        <v>5.159</v>
+        <v>6.158</v>
       </c>
       <c r="B102" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C102" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D102" s="7" t="n">
-        <v>7.278</v>
+        <v>7.2544</v>
       </c>
       <c r="E102" s="7" t="n">
-        <v>-2.8506</v>
+        <v>-2.6777</v>
       </c>
       <c r="F102" s="7" t="n">
-        <v>0.0039</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
-        <v>5.259</v>
+        <v>5.159</v>
       </c>
       <c r="B103" s="6" t="n">
         <v>5</v>
       </c>
       <c r="C103" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>7.297</v>
+        <v>7.278</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>-2.868</v>
+        <v>-2.8506</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>0.0018</v>
+        <v>0.0039</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
-        <v>4.16</v>
+        <v>5.259</v>
       </c>
       <c r="B104" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C104" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D104" s="7" t="n">
-        <v>7.2996</v>
+        <v>7.297</v>
       </c>
       <c r="E104" s="7" t="n">
-        <v>-3.0285</v>
+        <v>-2.868</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>0.003</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
-        <v>4.26</v>
+        <v>4.16</v>
       </c>
       <c r="B105" s="6" t="n">
         <v>4</v>
       </c>
       <c r="C105" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>7.3144</v>
+        <v>7.2996</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>-3.0355</v>
+        <v>-3.0285</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>0.0019</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n">
-        <v>3.161</v>
+        <v>4.26</v>
       </c>
       <c r="B106" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C106" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106" s="7" t="n">
-        <v>7.3184</v>
+        <v>7.3144</v>
       </c>
       <c r="E106" s="7" t="n">
-        <v>-3.2088</v>
+        <v>-3.0355</v>
       </c>
       <c r="F106" s="7" t="n">
-        <v>0.0022</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n">
-        <v>2.162</v>
+        <v>3.161</v>
       </c>
       <c r="B107" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C107" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>7.3292</v>
+        <v>7.3184</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>-3.3806</v>
+        <v>-3.2088</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>0.0008</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="n">
-        <v>3.261</v>
+        <v>2.162</v>
       </c>
       <c r="B108" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C108" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D108" s="7" t="n">
-        <v>7.3303</v>
+        <v>7.3292</v>
       </c>
       <c r="E108" s="7" t="n">
-        <v>-3.2122</v>
+        <v>-3.3806</v>
       </c>
       <c r="F108" s="7" t="n">
-        <v>0.002</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="n">
-        <v>2.262</v>
+        <v>3.261</v>
       </c>
       <c r="B109" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C109" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>7.3391</v>
+        <v>7.3303</v>
       </c>
       <c r="E109" s="7" t="n">
-        <v>-3.3829</v>
+        <v>-3.2122</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>0.0016</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="n">
-        <v>1.263</v>
+        <v>2.262</v>
       </c>
       <c r="B110" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C110" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D110" s="7" t="n">
-        <v>7.3415</v>
+        <v>7.3389</v>
       </c>
       <c r="E110" s="7" t="n">
-        <v>-3.5212</v>
+        <v>-3.3829</v>
       </c>
       <c r="F110" s="7" t="n">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="111">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="F115" s="10" t="n">
-        <v>1.833</v>
+        <v>1.8334</v>
       </c>
     </row>
   </sheetData>
